--- a/artfynd/A 58252-2025 artfynd.xlsx
+++ b/artfynd/A 58252-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131737823</v>
       </c>
       <c r="B2" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58252-2025 artfynd.xlsx
+++ b/artfynd/A 58252-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131737823</v>
       </c>
       <c r="B2" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58252-2025 artfynd.xlsx
+++ b/artfynd/A 58252-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131737823</v>
       </c>
       <c r="B2" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58252-2025 artfynd.xlsx
+++ b/artfynd/A 58252-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131737823</v>
       </c>
       <c r="B2" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58252-2025 artfynd.xlsx
+++ b/artfynd/A 58252-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131737823</v>
       </c>
       <c r="B2" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58252-2025 artfynd.xlsx
+++ b/artfynd/A 58252-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131737823</v>
       </c>
       <c r="B2" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58252-2025 artfynd.xlsx
+++ b/artfynd/A 58252-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131737823</v>
       </c>
       <c r="B2" t="n">
-        <v>93174</v>
+        <v>93210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58252-2025 artfynd.xlsx
+++ b/artfynd/A 58252-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131737823</v>
       </c>
       <c r="B2" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
